--- a/tabla_embalajes_paletizados.xlsx
+++ b/tabla_embalajes_paletizados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fer\IA\01 Optimización de cargas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DC4E2F7-B78C-43E3-B105-94C2E5B88126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047E7F13-C582-436F-9794-5B7C1EF5FC8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,24 +16,14 @@
     <sheet name="Embalajes Paletizados" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Embalajes Paletizados'!$A$5:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Embalajes Paletizados'!$A$1:$G$9</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
-  <si>
-    <t>EMBALAJES PALETIZADOS — TABLA DE INPUT</t>
-  </si>
-  <si>
-    <t>Tabla de referencia para embalajes que se transportan paletizados. Contiene el 7% de Part Numbers con menor huella de piso (Largo × Ancho) de la tabla de embalajes. Criterio: los embalajes deben caber dentro de un pallet europeo estándar (120×80 cm) y permitir al menos 2 pallets de altura dentro del camión (alto camión: 280 cm; altura útil por pallet: 125 cm; altura base pallet: 15 cm). Embalaje Paletizado = Embalaje_Origen concatenado con Cant. Embalajes por Pallet (separador: _). Cant. PNs por Embalaje Paletizado = Cant. PNs por Embalaje × Cant. Embalajes por Pallet.</t>
-  </si>
-  <si>
-    <t>← Columnas de verificación del cálculo (no son input del modelo)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t>DUNS
 Proveedor</t>
@@ -144,28 +134,19 @@
   </si>
   <si>
     <t>PN-073</t>
-  </si>
-  <si>
-    <t>Notas: (1) Pallet EUR/EPAL: 120×80 cm. (2) Altura base pallet: 15 cm. (3) Altura útil por pallet para 2 niveles en camión de 280 cm: 125 cm. (4) Se evaluaron ambas orientaciones de los embalajes sobre la huella del pallet. (5) Embalaje Paletizado = código del embalaje origen + "_" + cantidad de embalajes por pallet. (6) Cant. PNs por Embalaje Paletizado = Cant. PNs por Embalaje × Cant. Embalajes por Pallet. (7) Esta tabla es input futuro — el algoritmo actual no la consume.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <i/>
@@ -255,44 +236,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -599,7 +567,7 @@
   <sheetPr>
     <tabColor rgb="FF375623"/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -613,108 +581,217 @@
     <col min="10" max="12" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
+    <row r="2" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3">
+        <v>6</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="3">
+        <v>24</v>
+      </c>
+      <c r="H2" s="4">
+        <v>3</v>
+      </c>
+      <c r="I2" s="4">
+        <v>2</v>
+      </c>
+      <c r="J2" s="8">
+        <v>120</v>
+      </c>
+      <c r="K2" s="8">
+        <v>80</v>
+      </c>
+      <c r="L2" s="8">
+        <v>114</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
+    <row r="3" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="5">
+        <v>4</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="3">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="3">
+        <v>24</v>
+      </c>
+      <c r="H3" s="6">
+        <v>3</v>
+      </c>
+      <c r="I3" s="6">
+        <v>2</v>
+      </c>
+      <c r="J3" s="8">
+        <v>120</v>
+      </c>
+      <c r="K3" s="8">
+        <v>80</v>
+      </c>
+      <c r="L3" s="8">
+        <v>117</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H4" s="13" t="s">
+    <row r="4" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="3">
+        <v>6</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="3">
+        <v>30</v>
+      </c>
+      <c r="H4" s="4">
+        <v>3</v>
+      </c>
+      <c r="I4" s="4">
         <v>2</v>
       </c>
-      <c r="I4" s="10"/>
+      <c r="J4" s="8">
+        <v>120</v>
+      </c>
+      <c r="K4" s="8">
+        <v>80</v>
+      </c>
+      <c r="L4" s="8">
+        <v>117</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="5">
+        <v>12</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="3">
+        <v>6</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="3">
+        <v>72</v>
+      </c>
+      <c r="H5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>14</v>
+      <c r="I5" s="6">
+        <v>2</v>
+      </c>
+      <c r="J5" s="8">
+        <v>120</v>
+      </c>
+      <c r="K5" s="8">
+        <v>80</v>
+      </c>
+      <c r="L5" s="8">
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" s="3">
         <v>6</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6" s="3">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H6" s="4">
         <v>3</v>
@@ -729,33 +806,33 @@
         <v>80</v>
       </c>
       <c r="L6" s="8">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C7" s="5">
+        <v>12</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="3">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="3">
+        <v>96</v>
+      </c>
+      <c r="H7" s="6">
         <v>4</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="3">
-        <v>6</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="3">
-        <v>24</v>
-      </c>
-      <c r="H7" s="6">
-        <v>3</v>
       </c>
       <c r="I7" s="6">
         <v>2</v>
@@ -767,33 +844,33 @@
         <v>80</v>
       </c>
       <c r="L7" s="8">
-        <v>117</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E8" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G8" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H8" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" s="4">
         <v>2</v>
@@ -805,33 +882,33 @@
         <v>80</v>
       </c>
       <c r="L8" s="8">
-        <v>117</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C9" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E9" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G9" s="3">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H9" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" s="6">
         <v>2</v>
@@ -843,182 +920,11 @@
         <v>80</v>
       </c>
       <c r="L9" s="8">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="2">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="3">
-        <v>6</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="3">
-        <v>30</v>
-      </c>
-      <c r="H10" s="4">
-        <v>3</v>
-      </c>
-      <c r="I10" s="4">
-        <v>2</v>
-      </c>
-      <c r="J10" s="8">
-        <v>120</v>
-      </c>
-      <c r="K10" s="8">
-        <v>80</v>
-      </c>
-      <c r="L10" s="8">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="5">
-        <v>12</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="3">
-        <v>8</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="3">
-        <v>96</v>
-      </c>
-      <c r="H11" s="6">
-        <v>4</v>
-      </c>
-      <c r="I11" s="6">
-        <v>2</v>
-      </c>
-      <c r="J11" s="8">
-        <v>120</v>
-      </c>
-      <c r="K11" s="8">
-        <v>80</v>
-      </c>
-      <c r="L11" s="8">
         <v>139</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="2">
-        <v>4</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="3">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="3">
-        <v>32</v>
-      </c>
-      <c r="H12" s="4">
-        <v>4</v>
-      </c>
-      <c r="I12" s="4">
-        <v>2</v>
-      </c>
-      <c r="J12" s="8">
-        <v>120</v>
-      </c>
-      <c r="K12" s="8">
-        <v>80</v>
-      </c>
-      <c r="L12" s="8">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="5">
-        <v>10</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="3">
-        <v>8</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="3">
-        <v>80</v>
-      </c>
-      <c r="H13" s="6">
-        <v>4</v>
-      </c>
-      <c r="I13" s="6">
-        <v>2</v>
-      </c>
-      <c r="J13" s="8">
-        <v>120</v>
-      </c>
-      <c r="K13" s="8">
-        <v>80</v>
-      </c>
-      <c r="L13" s="8">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G13" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="4">
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A2:I3"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="H4:I4"/>
-  </mergeCells>
+  <autoFilter ref="A1:G9" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>